--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484212_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484212_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2852</v>
+        <v>5.6689</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9742</v>
+        <v>4.6302</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3111</v>
+        <v>1.0387</v>
       </c>
       <c r="G2" t="n">
         <v>4.6945</v>
@@ -610,13 +610,13 @@
         <v>2.5395</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0648</v>
+        <v>0.4485</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8118</v>
+        <v>0.4679</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2529</v>
+        <v>-0.0194</v>
       </c>
       <c r="V2" t="n">
         <v>-0.8415</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>F. ALVAREZ BACO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7192</v>
+        <v>0.5513</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5437</v>
+        <v>0.4522</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1755</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6463</v>
+        <v>0.7045</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0926</v>
+        <v>-0.2671</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5537</v>
+        <v>0.9716</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2214</v>
+        <v>1.7239</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3313</v>
+        <v>-0.0576</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5527</v>
+        <v>1.7815</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4249</v>
+        <v>-1.0194</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4239</v>
+        <v>-0.2095</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.001</v>
+        <v>-0.8099</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6074</v>
+        <v>-0.5619</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7418</v>
+        <v>-0.295</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1344</v>
+        <v>-0.2669</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2186</v>
+        <v>-0.1773</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2186</v>
+        <v>-0.1773</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. ALVAREZ BACO</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6912</v>
+        <v>0.3657</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7554999999999999</v>
+        <v>-0.6298</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0643</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7045</v>
+        <v>-1.4055</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2671</v>
+        <v>-1.1218</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9716</v>
+        <v>-0.2837</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7239</v>
+        <v>-0.3761</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0576</v>
+        <v>-1.0374</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7815</v>
+        <v>0.6613</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0194</v>
+        <v>-1.0293</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2095</v>
+        <v>-0.0844</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8099</v>
+        <v>-0.9449</v>
       </c>
       <c r="P4" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.422</v>
+        <v>0.013</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0083</v>
+        <v>-0.2537</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4303</v>
+        <v>0.2667</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1773</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>M. TOLEDO CIVICO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3443</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.1959</v>
+        <v>-0.1331</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5402</v>
+        <v>0.2176</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.4055</v>
+        <v>-0.7145</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.1218</v>
+        <v>-0.2287</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2837</v>
+        <v>-0.4858</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3761</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.0374</v>
+        <v>-0.6332</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6613</v>
+        <v>0.7284</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0293</v>
+        <v>-0.8097</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0844</v>
+        <v>0.4045</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9449</v>
+        <v>-1.2142</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0083</v>
+        <v>-0.4512</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8198</v>
+        <v>-0.2283</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8114</v>
+        <v>-0.2229</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. TOLEDO CIVICO</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0245</v>
+        <v>-0.3689</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1331</v>
+        <v>0.9604</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1087</v>
+        <v>-1.3293</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7145</v>
+        <v>-0.2817</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2287</v>
+        <v>1.7552</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4858</v>
+        <v>-2.0369</v>
       </c>
       <c r="J6" t="n">
-        <v>0.09520000000000001</v>
+        <v>1.7011</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6332</v>
+        <v>2.9279</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7284</v>
+        <v>-1.2268</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8097</v>
+        <v>-1.9828</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4045</v>
+        <v>-1.1727</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2142</v>
+        <v>-0.8101</v>
       </c>
       <c r="P6" t="n">
-        <v>0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.1488</v>
       </c>
       <c r="R6" t="n">
-        <v>0.586</v>
+        <v>1.9534</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5601</v>
+        <v>0.4403</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2283</v>
+        <v>0.5215</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3318</v>
+        <v>-0.0813</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6642</v>
+        <v>-0.3321</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6642</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4623</v>
+        <v>-0.4803</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6707</v>
+        <v>-0.7103</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.133</v>
+        <v>0.23</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1533</v>
+        <v>-0.6463</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4792</v>
+        <v>-0.0926</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.6324</v>
+        <v>-0.5537</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0846</v>
+        <v>-0.2214</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.3313</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1214</v>
+        <v>-0.5527</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.2379</v>
+        <v>-0.4249</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.484</v>
+        <v>-0.4239</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7538</v>
+        <v>-0.001</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1953</v>
+        <v>0.9767</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9767</v>
+        <v>1.9534</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3318</v>
+        <v>0.4079</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2037</v>
+        <v>0.4878</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1281</v>
+        <v>-0.0799</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5545</v>
+        <v>-1.2186</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9483</v>
+        <v>-0.9757</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3537</v>
+        <v>0.2662</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.302</v>
+        <v>-1.2419</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2817</v>
+        <v>-1.1533</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7552</v>
+        <v>0.4792</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.0369</v>
+        <v>-1.6324</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7011</v>
+        <v>1.0846</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9279</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2268</v>
+        <v>0.1214</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9828</v>
+        <v>-2.2379</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1727</v>
+        <v>-0.484</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8101</v>
+        <v>-1.7538</v>
       </c>
       <c r="P8" t="n">
         <v>-0.1953</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9534</v>
+        <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1392</v>
+        <v>-0.1816</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0851</v>
+        <v>-0.2008</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0541</v>
+        <v>0.0192</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3321</v>
+        <v>0.5545</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8865</v>
+        <v>0.5545</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5343</v>
+        <v>-1.8732</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7743</v>
+        <v>-1.1676</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7601</v>
+        <v>-0.7056</v>
       </c>
       <c r="G9" t="n">
         <v>-3.0674</v>
@@ -1156,13 +1156,13 @@
         <v>2.1488</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2663</v>
+        <v>0.3949</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4015</v>
+        <v>0.2052</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1352</v>
+        <v>0.1897</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1773</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>G. LOZANO MASSANET</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2319</v>
+        <v>-2.1149</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3159</v>
+        <v>-3.469</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.916</v>
+        <v>1.3542</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1709</v>
+        <v>-3.6847</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4421</v>
+        <v>-2.7808</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7288</v>
+        <v>-0.9039</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8771</v>
+        <v>-3.1254</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9581</v>
+        <v>-1.8176</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0809</v>
+        <v>-1.3077</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2937</v>
+        <v>-0.5593</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.484</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8097</v>
+        <v>0.4039</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.7581</v>
+        <v>1.7581</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9301</v>
+        <v>-0.1953</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1721</v>
+        <v>1.9534</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4836</v>
+        <v>0.1438</v>
       </c>
       <c r="T10" t="n">
-        <v>1.4914</v>
+        <v>0.1838</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0077</v>
+        <v>-0.04</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.7866</v>
+        <v>-0.3321</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.7866</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. LOZANO MASSANET</t>
+          <t>O. ROSA BEJARANO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.385</v>
+        <v>-3.3583</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4396</v>
+        <v>-2.1078</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0546</v>
+        <v>-1.2505</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.6847</v>
+        <v>-2.2404</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.7808</v>
+        <v>-0.7572</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9039</v>
+        <v>-1.4832</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.1254</v>
+        <v>-1.3469</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.8176</v>
+        <v>0.0013</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3077</v>
+        <v>-1.3482</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5593</v>
+        <v>-0.8935</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-0.7585</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4039</v>
+        <v>-0.135</v>
       </c>
       <c r="P11" t="n">
-        <v>1.7581</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.1953</v>
+        <v>-1.9534</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9534</v>
+        <v>0.1953</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1264</v>
+        <v>0.3081</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.0261</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3396</v>
+        <v>0.3342</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3321</v>
+        <v>0.3321</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3321</v>
+        <v>1.2186</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O. ROSA BEJARANO</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4788</v>
+        <v>-3.5874</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.31</v>
+        <v>-2.8621</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1688</v>
+        <v>-0.7254</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.2404</v>
+        <v>-2.1709</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7572</v>
+        <v>-1.4421</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.4832</v>
+        <v>-0.7288</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.3469</v>
+        <v>-0.8771</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0013</v>
+        <v>-0.9581</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3482</v>
+        <v>0.0809</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8935</v>
+        <v>-1.2937</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7585</v>
+        <v>-0.484</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.135</v>
+        <v>-0.8097</v>
       </c>
       <c r="P12" t="n">
         <v>-1.7581</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1876</v>
+        <v>1.1281</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2283</v>
+        <v>0.9452</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4159</v>
+        <v>0.1829</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3321</v>
+        <v>-0.7866</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8865</v>
+        <v>-0.7866</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.3858</v>
+        <v>-4.0202</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.1867</v>
+        <v>-1.9845</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1991</v>
+        <v>-2.0357</v>
       </c>
       <c r="G13" t="n">
         <v>-3.1478</v>
@@ -1468,13 +1468,13 @@
         <v>0.7814</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-0.5351</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6052</v>
+        <v>-0.403</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2955</v>
+        <v>-0.1321</v>
       </c>
       <c r="V13" t="n">
         <v>-1.1187</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.411</v>
+        <v>-10.1085</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.057700000000001</v>
+        <v>-6.755199999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.3532</v>
+        <v>-3.3533</v>
       </c>
       <c r="G14" t="n">
         <v>-13.1135</v>
       </c>
       <c r="H14" t="n">
-        <v>-7.715599999999999</v>
+        <v>-7.7156</v>
       </c>
       <c r="I14" t="n">
         <v>-5.3977</v>
@@ -1522,7 +1522,7 @@
         <v>2.597</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.7804000000000001</v>
+        <v>-0.7803999999999999</v>
       </c>
       <c r="L14" t="n">
         <v>3.3775</v>
@@ -1537,7 +1537,7 @@
         <v>-8.775</v>
       </c>
       <c r="P14" t="n">
-        <v>4.8836</v>
+        <v>4.883599999999999</v>
       </c>
       <c r="Q14" t="n">
         <v>-12.6973</v>
@@ -1546,13 +1546,13 @@
         <v>17.5808</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2522</v>
+        <v>1.5548</v>
       </c>
       <c r="T14" t="n">
-        <v>1.102</v>
+        <v>1.4045</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1501</v>
+        <v>0.1502</v>
       </c>
       <c r="V14" t="n">
         <v>-3.4334</v>
@@ -1561,7 +1561,7 @@
         <v>1.9405</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.3739</v>
+        <v>-5.373899999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>11.435</v>
+        <v>11.5375</v>
       </c>
       <c r="E15" t="n">
-        <v>10.9494</v>
+        <v>10.646</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4857</v>
+        <v>0.8915</v>
       </c>
       <c r="G15" t="n">
         <v>8.0884</v>
@@ -1624,13 +1624,13 @@
         <v>2.1488</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4347</v>
+        <v>-0.3323</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3193</v>
+        <v>0.016</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.754</v>
+        <v>-0.3482</v>
       </c>
       <c r="V15" t="n">
         <v>1.8279</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.798</v>
+        <v>3.6152</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7112</v>
+        <v>2.61</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0869</v>
+        <v>1.0052</v>
       </c>
       <c r="G16" t="n">
         <v>4.5289</v>
@@ -1702,13 +1702,13 @@
         <v>1.1721</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2811</v>
+        <v>0.0983</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0689</v>
+        <v>-0.0322</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2122</v>
+        <v>0.1305</v>
       </c>
       <c r="V16" t="n">
         <v>0.9414</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2548</v>
+        <v>2.1666</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6353</v>
+        <v>1.3319</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.8347</v>
       </c>
       <c r="G17" t="n">
         <v>2.9046</v>
@@ -1780,13 +1780,13 @@
         <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0639</v>
+        <v>-0.152</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3798</v>
+        <v>0.0765</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4437</v>
+        <v>-0.2285</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8972</v>
+        <v>1.4184</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2039</v>
+        <v>-0.481</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6933</v>
+        <v>1.8994</v>
       </c>
       <c r="G18" t="n">
-        <v>2.5679</v>
+        <v>1.2757</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7311</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8368</v>
+        <v>2.1583</v>
       </c>
       <c r="J18" t="n">
-        <v>2.2031</v>
+        <v>1.78</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5003</v>
+        <v>-0.2443</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7027</v>
+        <v>2.0243</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3648</v>
+        <v>-0.5042</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2308</v>
+        <v>-0.6382</v>
       </c>
       <c r="O18" t="n">
         <v>0.134</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3907</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.5395</v>
+        <v>-3.5162</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2707</v>
+        <v>0.4635</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8724</v>
+        <v>-0.2406</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6017</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.5507</v>
+        <v>1.8279</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3321</v>
+        <v>1.4959</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2186</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>S. NDOYE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8948</v>
+        <v>1.0751</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0877</v>
+        <v>-0.5339</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9825</v>
+        <v>1.609</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2757</v>
+        <v>0.0862</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8826000000000001</v>
+        <v>0.9496</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1583</v>
+        <v>-0.8633999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>1.78</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2443</v>
+        <v>1.1883</v>
       </c>
       <c r="L19" t="n">
-        <v>2.0243</v>
+        <v>-0.458</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5042</v>
+        <v>-0.6441</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6382</v>
+        <v>-0.2386</v>
       </c>
       <c r="O19" t="n">
-        <v>0.134</v>
+        <v>-0.4054</v>
       </c>
       <c r="P19" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-2.1488</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-3.5162</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.3674</v>
+        <v>2.3441</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0601</v>
+        <v>-0.4251</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.3341</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7872</v>
+        <v>-0.091</v>
       </c>
       <c r="V19" t="n">
-        <v>1.8279</v>
+        <v>1.2186</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4959</v>
+        <v>1.2186</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. NDOYE</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.847</v>
+        <v>0.5329</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7362</v>
+        <v>-0.4028</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5831</v>
+        <v>0.9357</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0862</v>
+        <v>2.5679</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9496</v>
+        <v>1.7311</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8633999999999999</v>
+        <v>0.8368</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7302999999999999</v>
+        <v>2.2031</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1883</v>
+        <v>1.5003</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.458</v>
+        <v>0.7027</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6441</v>
+        <v>0.3648</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2386</v>
+        <v>0.2308</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4054</v>
+        <v>0.134</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1488</v>
+        <v>-2.5395</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3441</v>
+        <v>2.1488</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6532</v>
+        <v>-0.0936</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5364</v>
+        <v>0.2657</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1169</v>
+        <v>-0.3593</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2186</v>
+        <v>-1.5507</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2186</v>
+        <v>-0.3321</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="21">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4734</v>
+        <v>-1.9328</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8057</v>
+        <v>-1.4012</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6677</v>
+        <v>-0.5315</v>
       </c>
       <c r="G22" t="n">
         <v>-1.9919</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2861</v>
+        <v>0.2545</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3026</v>
+        <v>0.1018</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0165</v>
+        <v>0.1527</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8445</v>
+        <v>-2.8912</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8387</v>
+        <v>-3.9398</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9942</v>
+        <v>1.0486</v>
       </c>
       <c r="G23" t="n">
         <v>-2.6855</v>
@@ -2248,13 +2248,13 @@
         <v>0.7814</v>
       </c>
       <c r="S23" t="n">
-        <v>0.427</v>
+        <v>0.3804</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1294</v>
+        <v>0.0283</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2976</v>
+        <v>0.3521</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.9324</v>
+        <v>-3.2971</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.6175</v>
+        <v>-4.4153</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6851</v>
+        <v>1.1182</v>
       </c>
       <c r="G24" t="n">
         <v>-1.2562</v>
@@ -2326,13 +2326,13 @@
         <v>1.1721</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6724</v>
+        <v>-0.0371</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1732</v>
+        <v>0.029</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4992</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-0.8317</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>10.4113</v>
+        <v>11.7594</v>
       </c>
       <c r="E25" t="n">
-        <v>3.3535</v>
+        <v>3.353399999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>7.057900000000001</v>
+        <v>8.4061</v>
       </c>
       <c r="G25" t="n">
         <v>13.1134</v>
@@ -2374,7 +2374,7 @@
         <v>7.715599999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>5.397599999999999</v>
+        <v>5.397600000000001</v>
       </c>
       <c r="J25" t="n">
         <v>15.7104</v>
@@ -2389,7 +2389,7 @@
         <v>-2.597</v>
       </c>
       <c r="N25" t="n">
-        <v>0.7807000000000003</v>
+        <v>0.7807000000000001</v>
       </c>
       <c r="O25" t="n">
         <v>-3.3775</v>
@@ -2404,13 +2404,13 @@
         <v>12.6974</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2521</v>
+        <v>0.0961000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1502000000000001</v>
+        <v>-0.1501</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.102</v>
+        <v>0.2461999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>3.4334</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484212_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484212_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,47 +549,52 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. GONZÁLEZ BRUMOS</t>
+          <t>P. GONZALEZ BRUMOS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6689</v>
+        <v>3.234</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6302</v>
+        <v>2.1953</v>
       </c>
       <c r="F2" t="n">
         <v>1.0387</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6945</v>
+        <v>2.2596</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7429</v>
+        <v>0.1289</v>
       </c>
       <c r="I2" t="n">
-        <v>3.9516</v>
+        <v>2.1307</v>
       </c>
       <c r="J2" t="n">
-        <v>5.9985</v>
+        <v>3.5636</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6411</v>
+        <v>1.0271</v>
       </c>
       <c r="L2" t="n">
-        <v>4.3575</v>
+        <v>2.5365</v>
       </c>
       <c r="M2" t="n">
         <v>-1.304</v>
@@ -626,1104 +631,1175 @@
       </c>
       <c r="X2" t="n">
         <v>-0.1773</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484212_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. ALVAREZ BACO</t>
+          <t>P. GONZÁLEZ BRUMOS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5513</v>
+        <v>2.4349</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4522</v>
+        <v>2.4349</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09909999999999999</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7045</v>
+        <v>2.4349</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2671</v>
+        <v>0.614</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9716</v>
+        <v>1.821</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7239</v>
+        <v>2.4349</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0576</v>
+        <v>0.614</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7815</v>
+        <v>1.821</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0194</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2095</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8099</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5619</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.295</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2669</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1773</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1773</v>
+        <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484212_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>F. ALVAREZ BACO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3657</v>
+        <v>0.5513</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6298</v>
+        <v>0.4522</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9955000000000001</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.4055</v>
+        <v>0.7045</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1218</v>
+        <v>-0.2671</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2837</v>
+        <v>0.9716</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.3761</v>
+        <v>1.7239</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.0374</v>
+        <v>-0.0576</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6613</v>
+        <v>1.7815</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0293</v>
+        <v>-1.0194</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0844</v>
+        <v>-0.2095</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9449</v>
+        <v>-0.8099</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S4" t="n">
-        <v>0.013</v>
+        <v>-0.5619</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2537</v>
+        <v>-0.295</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2667</v>
+        <v>-0.2669</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.1773</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1773</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484212_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. TOLEDO CIVICO</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.307</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1331</v>
+        <v>0.307</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2176</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7145</v>
+        <v>0.307</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2287</v>
+        <v>0.307</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4858</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.307</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6332</v>
+        <v>0.307</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7284</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8097</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4045</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2142</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4512</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2283</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2229</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484212_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>M. TOLEDO CIVICO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3689</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9604</v>
+        <v>-0.1331</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3293</v>
+        <v>0.2176</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2817</v>
+        <v>-0.7145</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7552</v>
+        <v>-0.2287</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.0369</v>
+        <v>-0.4858</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7011</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9279</v>
+        <v>-0.6332</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2268</v>
+        <v>0.7284</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9828</v>
+        <v>-0.8097</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1727</v>
+        <v>0.4045</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8101</v>
+        <v>-1.2142</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9534</v>
+        <v>0.586</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4403</v>
+        <v>-0.4512</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5215</v>
+        <v>-0.2283</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0813</v>
+        <v>-0.2229</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3321</v>
+        <v>0.6642</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2186</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484212_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>E. MARTIN GASCON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4803</v>
+        <v>0.0587</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7103</v>
+        <v>-0.9368</v>
       </c>
       <c r="F7" t="n">
-        <v>0.23</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6463</v>
+        <v>-1.7124</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0926</v>
+        <v>-1.4288</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5537</v>
+        <v>-0.2837</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2214</v>
+        <v>-0.6831</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3313</v>
+        <v>-1.3444</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5527</v>
+        <v>0.6613</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4249</v>
+        <v>-1.0293</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4239</v>
+        <v>-0.0844</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.001</v>
+        <v>-0.9449</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9534</v>
+        <v>1.7581</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4079</v>
+        <v>0.013</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4878</v>
+        <v>-0.2537</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0799</v>
+        <v>0.2667</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484212_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9757</v>
+        <v>-0.3689</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2662</v>
+        <v>0.9604</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2419</v>
+        <v>-1.3293</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1533</v>
+        <v>-0.2817</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4792</v>
+        <v>1.7552</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6324</v>
+        <v>-2.0369</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0846</v>
+        <v>1.7011</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9631999999999999</v>
+        <v>2.9279</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1214</v>
+        <v>-1.2268</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2379</v>
+        <v>-1.9828</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.484</v>
+        <v>-1.1727</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.7538</v>
+        <v>-0.8101</v>
       </c>
       <c r="P8" t="n">
         <v>-0.1953</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1721</v>
+        <v>-2.1488</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9767</v>
+        <v>1.9534</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1816</v>
+        <v>0.4403</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2008</v>
+        <v>0.5215</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0192</v>
+        <v>-0.0813</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5545</v>
+        <v>-0.3321</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5545</v>
+        <v>0.8865</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484212_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8732</v>
+        <v>-0.4803</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1676</v>
+        <v>-0.7103</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7056</v>
+        <v>0.23</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.0674</v>
+        <v>-0.6463</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.8353</v>
+        <v>-0.0926</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7679</v>
+        <v>-0.5537</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2007</v>
+        <v>-0.2214</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.1835</v>
+        <v>0.3313</v>
       </c>
       <c r="L9" t="n">
-        <v>1.9828</v>
+        <v>-0.5527</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.8668</v>
+        <v>-0.4249</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.6518</v>
+        <v>-0.4239</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.215</v>
+        <v>-0.001</v>
       </c>
       <c r="P9" t="n">
         <v>0.9767</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1488</v>
+        <v>1.9534</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3949</v>
+        <v>0.4079</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2052</v>
+        <v>0.4878</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1897</v>
+        <v>-0.0799</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1773</v>
+        <v>-1.2186</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1773</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484212_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. LOZANO MASSANET</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1149</v>
+        <v>-0.9757</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.469</v>
+        <v>0.2662</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3542</v>
+        <v>-1.2419</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.6847</v>
+        <v>-1.1533</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.7808</v>
+        <v>0.4792</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9039</v>
+        <v>-1.6324</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.1254</v>
+        <v>1.0846</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.8176</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3077</v>
+        <v>0.1214</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5593</v>
+        <v>-2.2379</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-0.484</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4039</v>
+        <v>-1.7538</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7581</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9534</v>
+        <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1438</v>
+        <v>-0.1816</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1838</v>
+        <v>-0.2008</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.04</v>
+        <v>0.0192</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3321</v>
+        <v>0.5545</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3321</v>
+        <v>0.5545</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484212_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. ROSA BEJARANO</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3583</v>
+        <v>-1.8732</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1078</v>
+        <v>-1.1676</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2505</v>
+        <v>-0.7056</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2404</v>
+        <v>-3.0674</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7572</v>
+        <v>-3.8353</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4832</v>
+        <v>0.7679</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3469</v>
+        <v>-0.2007</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0013</v>
+        <v>-2.1835</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3482</v>
+        <v>1.9828</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8935</v>
+        <v>-2.8668</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7585</v>
+        <v>-1.6518</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.135</v>
+        <v>-1.215</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9534</v>
+        <v>-1.1721</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1953</v>
+        <v>2.1488</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3081</v>
+        <v>0.3949</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0261</v>
+        <v>0.2052</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3342</v>
+        <v>0.1897</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3321</v>
+        <v>-0.1773</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8865</v>
+        <v>-0.1773</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484212_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>G. LOZANO MASSANET</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5874</v>
+        <v>-2.1149</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8621</v>
+        <v>-3.469</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7254</v>
+        <v>1.3542</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.1709</v>
+        <v>-3.6847</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.4421</v>
+        <v>-2.7808</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7288</v>
+        <v>-0.9039</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8771</v>
+        <v>-3.1254</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9581</v>
+        <v>-1.8176</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0809</v>
+        <v>-1.3077</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2937</v>
+        <v>-0.5593</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.484</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8097</v>
+        <v>0.4039</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.7581</v>
+        <v>1.7581</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.9301</v>
+        <v>-0.1953</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1721</v>
+        <v>1.9534</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1281</v>
+        <v>0.1438</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9452</v>
+        <v>0.1838</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1829</v>
+        <v>-0.04</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.7866</v>
+        <v>-0.3321</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.7866</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484212_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>O. ROSA BEJARANO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.0202</v>
+        <v>-3.3583</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.9845</v>
+        <v>-2.1078</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0357</v>
+        <v>-1.2505</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.1478</v>
+        <v>-2.2404</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1673</v>
+        <v>-0.7572</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.9804</v>
+        <v>-1.4832</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.8587</v>
+        <v>-1.3469</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0422</v>
+        <v>0.0013</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.9009</v>
+        <v>-1.3482</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.2891</v>
+        <v>-0.8935</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2095</v>
+        <v>-0.7585</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0795</v>
+        <v>-0.135</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7814</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5351</v>
+        <v>0.3081</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.403</v>
+        <v>-0.0261</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1321</v>
+        <v>0.3342</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.1187</v>
+        <v>0.3321</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.3959</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484212_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.1085</v>
+        <v>-3.5874</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.755199999999999</v>
+        <v>-2.8621</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.3533</v>
+        <v>-0.7254</v>
       </c>
       <c r="G14" t="n">
-        <v>-13.1135</v>
+        <v>-2.1709</v>
       </c>
       <c r="H14" t="n">
-        <v>-7.7156</v>
+        <v>-1.4421</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.3977</v>
+        <v>-0.7288</v>
       </c>
       <c r="J14" t="n">
-        <v>2.597</v>
+        <v>-0.8771</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.7803999999999999</v>
+        <v>-0.9581</v>
       </c>
       <c r="L14" t="n">
-        <v>3.3775</v>
+        <v>0.0809</v>
       </c>
       <c r="M14" t="n">
-        <v>-15.7104</v>
+        <v>-1.2937</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.935199999999999</v>
+        <v>-0.484</v>
       </c>
       <c r="O14" t="n">
-        <v>-8.775</v>
+        <v>-0.8097</v>
       </c>
       <c r="P14" t="n">
-        <v>4.883599999999999</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q14" t="n">
-        <v>-12.6973</v>
+        <v>-2.9301</v>
       </c>
       <c r="R14" t="n">
-        <v>17.5808</v>
+        <v>1.1721</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5548</v>
+        <v>1.1281</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4045</v>
+        <v>0.9452</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1502</v>
+        <v>0.1829</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.4334</v>
+        <v>-0.7866</v>
       </c>
       <c r="W14" t="n">
-        <v>1.9405</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.373899999999999</v>
+        <v>-0.7866</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484212_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. HERNANDEZ GIMENEZ</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>11.5375</v>
+        <v>-4.0202</v>
       </c>
       <c r="E15" t="n">
-        <v>10.646</v>
+        <v>-1.9845</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8915</v>
+        <v>-2.0357</v>
       </c>
       <c r="G15" t="n">
-        <v>8.0884</v>
+        <v>-3.1478</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1535</v>
+        <v>-0.1673</v>
       </c>
       <c r="I15" t="n">
-        <v>5.9348</v>
+        <v>-2.9804</v>
       </c>
       <c r="J15" t="n">
-        <v>8.3881</v>
+        <v>-1.8587</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3737</v>
+        <v>0.0422</v>
       </c>
       <c r="L15" t="n">
-        <v>7.0144</v>
+        <v>-1.9009</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2998</v>
+        <v>-1.2891</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7798</v>
+        <v>-0.2095</v>
       </c>
       <c r="O15" t="n">
         <v>-1.0795</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9534</v>
+        <v>0.7814</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1488</v>
+        <v>0.7814</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3323</v>
+        <v>-0.5351</v>
       </c>
       <c r="T15" t="n">
-        <v>0.016</v>
+        <v>-0.403</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3482</v>
+        <v>-0.1321</v>
       </c>
       <c r="V15" t="n">
-        <v>1.8279</v>
+        <v>-1.1187</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4373</v>
+        <v>0.2772</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6093</v>
+        <v>-1.3959</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484212_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. GASCON TORNE</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.6152</v>
+        <v>-10.1085</v>
       </c>
       <c r="E16" t="n">
-        <v>2.61</v>
+        <v>-6.755199999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0052</v>
+        <v>-3.3533</v>
       </c>
       <c r="G16" t="n">
-        <v>4.5289</v>
+        <v>-13.1134</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9261</v>
+        <v>-7.7156</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6028</v>
+        <v>-5.397600000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>4.5491</v>
+        <v>2.597</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9455</v>
+        <v>-0.7804000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>2.6036</v>
+        <v>3.3775</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0202</v>
+        <v>-15.7104</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0194</v>
+        <v>-6.935199999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0008</v>
+        <v>-8.775</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.9534</v>
+        <v>4.8836</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.1255</v>
+        <v>-12.6973</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1721</v>
+        <v>17.5808</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0983</v>
+        <v>1.5548</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0322</v>
+        <v>1.4045</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1305</v>
+        <v>0.1502</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9414</v>
+        <v>-3.4334</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2186</v>
+        <v>1.9405</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
-      </c>
+        <v>-5.3739</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>J. HERNANDEZ GIMENEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1666</v>
+        <v>11.5375</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3319</v>
+        <v>10.646</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8347</v>
+        <v>0.8915</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9046</v>
+        <v>8.0884</v>
       </c>
       <c r="H17" t="n">
-        <v>2.877</v>
+        <v>2.1535</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0276</v>
+        <v>5.9348</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4042</v>
+        <v>8.3881</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0274</v>
+        <v>1.3737</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3768</v>
+        <v>7.0144</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4996</v>
+        <v>-0.2998</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8496</v>
+        <v>0.7798</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3492</v>
+        <v>-1.0795</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.586</v>
+        <v>1.9534</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5627</v>
+        <v>2.1488</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.152</v>
+        <v>-0.3323</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0765</v>
+        <v>0.016</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2285</v>
+        <v>-0.3482</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484212_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>J. GASCON TORNE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4184</v>
+        <v>3.6152</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.481</v>
+        <v>2.61</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8994</v>
+        <v>1.0052</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2757</v>
+        <v>4.5289</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8826000000000001</v>
+        <v>1.9261</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1583</v>
+        <v>2.6028</v>
       </c>
       <c r="J18" t="n">
-        <v>1.78</v>
+        <v>4.5491</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2443</v>
+        <v>1.9455</v>
       </c>
       <c r="L18" t="n">
-        <v>2.0243</v>
+        <v>2.6036</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5042</v>
+        <v>-0.0202</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6382</v>
+        <v>-0.0194</v>
       </c>
       <c r="O18" t="n">
-        <v>0.134</v>
+        <v>-0.0008</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.1488</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.5162</v>
+        <v>-3.1255</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4635</v>
+        <v>0.0983</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2406</v>
+        <v>-0.0322</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.1305</v>
       </c>
       <c r="V18" t="n">
-        <v>1.8279</v>
+        <v>0.9414</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4959</v>
+        <v>1.2186</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3321</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484212_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. NDOYE</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0751</v>
+        <v>1.4184</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5339</v>
+        <v>-0.481</v>
       </c>
       <c r="F19" t="n">
-        <v>1.609</v>
+        <v>1.8994</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0862</v>
+        <v>1.2757</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9496</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8633999999999999</v>
+        <v>2.1583</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7302999999999999</v>
+        <v>1.78</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1883</v>
+        <v>-0.2443</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.458</v>
+        <v>2.0243</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6441</v>
+        <v>-0.5042</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2386</v>
+        <v>-0.6382</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4054</v>
+        <v>0.134</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1953</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1488</v>
+        <v>-3.5162</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3441</v>
+        <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4251</v>
+        <v>0.4635</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3341</v>
+        <v>-0.2406</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.091</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2186</v>
+        <v>1.8279</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2186</v>
+        <v>1.4959</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484212_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5329</v>
+        <v>1.2526</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4028</v>
+        <v>0.4179</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9357</v>
+        <v>0.8347</v>
       </c>
       <c r="G20" t="n">
-        <v>2.5679</v>
+        <v>1.9907</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7311</v>
+        <v>2.57</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8368</v>
+        <v>-0.5794</v>
       </c>
       <c r="J20" t="n">
-        <v>2.2031</v>
+        <v>2.4902</v>
       </c>
       <c r="K20" t="n">
-        <v>1.5003</v>
+        <v>1.7204</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7027</v>
+        <v>0.7698</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3648</v>
+        <v>-0.4996</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2308</v>
+        <v>0.8496</v>
       </c>
       <c r="O20" t="n">
-        <v>0.134</v>
+        <v>-1.3492</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3907</v>
+        <v>-0.586</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.5395</v>
+        <v>-2.1488</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1488</v>
+        <v>1.5627</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0936</v>
+        <v>-0.152</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2657</v>
+        <v>0.0765</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3593</v>
+        <v>-0.2285</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.5507</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484212_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. TALTAVULL BALLE</t>
+          <t>S. NDOYE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4652</v>
+        <v>1.0751</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0605</v>
+        <v>-0.5339</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4047</v>
+        <v>1.609</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4047</v>
+        <v>0.0862</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.9496</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4047</v>
+        <v>-0.8633999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1.1883</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.458</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4047</v>
+        <v>-0.6441</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-0.2386</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4047</v>
+        <v>-0.4054</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.1953</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.1488</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.3441</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0605</v>
+        <v>-0.4251</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0605</v>
+        <v>-0.3341</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>-0.091</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484212_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. BAGUR PONS</t>
+          <t>G. GARCÍA RIERA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2226,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9328</v>
+        <v>0.914</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4012</v>
+        <v>0.914</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5315</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9919</v>
+        <v>0.914</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9534</v>
+        <v>0.307</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0385</v>
+        <v>0.607</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3077</v>
+        <v>0.914</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6741</v>
+        <v>0.307</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.607</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6842</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2793</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4049</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2545</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1018</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1527</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2186,12 +2287,17 @@
       </c>
       <c r="X22" t="n">
         <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484212_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8912</v>
+        <v>0.5329</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.9398</v>
+        <v>-0.4028</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0486</v>
+        <v>0.9357</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.6855</v>
+        <v>2.5679</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5417999999999999</v>
+        <v>1.7311</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.1437</v>
+        <v>0.8368</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.6007</v>
+        <v>2.2031</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0819</v>
+        <v>1.5003</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.6826</v>
+        <v>0.7027</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0848</v>
+        <v>0.3648</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6237</v>
+        <v>0.2308</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5389</v>
+        <v>0.134</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.3674</v>
+        <v>-2.5395</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7814</v>
+        <v>2.1488</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3804</v>
+        <v>-0.0936</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0283</v>
+        <v>0.2657</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3521</v>
+        <v>-0.3593</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.5507</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484212_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>P. TALTAVULL BALLE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2971</v>
+        <v>-0.4652</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.4153</v>
+        <v>-0.0605</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1182</v>
+        <v>-0.4047</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.2562</v>
+        <v>-0.4047</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4561</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.7124</v>
+        <v>-0.4047</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.436</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.2635</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.1725</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1798</v>
+        <v>-0.4047</v>
       </c>
       <c r="N24" t="n">
-        <v>0.7197</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5399</v>
+        <v>-0.4047</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.3441</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0371</v>
+        <v>-0.0605</v>
       </c>
       <c r="T24" t="n">
-        <v>0.029</v>
+        <v>-0.0605</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.06619999999999999</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.8317</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1675</v>
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484212_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. BAGUR PONS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,318 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
+        <v>-1.9328</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-1.4012</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.5315</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.9919</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.9534</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-1.0385</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-1.3077</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.6741</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.6336000000000001</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.6842</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.2793</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.4049</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.2545</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.1018</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.1527</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484212_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>L. ANDUJAR MASCARO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-2.8912</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-3.9398</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.0486</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-2.6855</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.5417999999999999</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-2.1437</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-2.6007</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.0819</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-2.6826</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.0848</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.6237</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.5389</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-1.3674</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.3804</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.0283</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484212_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>R. GOMEZ PRIVAT</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-3.2971</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-4.4153</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.1182</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-1.2562</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.4561</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-1.7124</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-1.436</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.2635</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-1.1725</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.1798</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.7197</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.5399</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-2.3441</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.0371</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.06619999999999999</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-0.8317</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-0.1675</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484212_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
         <v>11.7594</v>
       </c>
-      <c r="E25" t="n">
-        <v>3.353399999999999</v>
-      </c>
-      <c r="F25" t="n">
-        <v>8.4061</v>
-      </c>
-      <c r="G25" t="n">
-        <v>13.1134</v>
-      </c>
-      <c r="H25" t="n">
+      <c r="E28" t="n">
+        <v>3.353400000000001</v>
+      </c>
+      <c r="F28" t="n">
+        <v>8.406099999999999</v>
+      </c>
+      <c r="G28" t="n">
+        <v>13.1135</v>
+      </c>
+      <c r="H28" t="n">
         <v>7.715599999999999</v>
       </c>
-      <c r="I25" t="n">
-        <v>5.397600000000001</v>
-      </c>
-      <c r="J25" t="n">
+      <c r="I28" t="n">
+        <v>5.397599999999999</v>
+      </c>
+      <c r="J28" t="n">
         <v>15.7104</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K28" t="n">
         <v>6.9352</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L28" t="n">
         <v>8.775100000000002</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M28" t="n">
         <v>-2.597</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N28" t="n">
         <v>0.7807000000000001</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O28" t="n">
         <v>-3.3775</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P28" t="n">
         <v>-4.883599999999999</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q28" t="n">
         <v>-17.5809</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R28" t="n">
         <v>12.6974</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S28" t="n">
         <v>0.0961000000000001</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T28" t="n">
         <v>-0.1501</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U28" t="n">
         <v>0.2461999999999999</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V28" t="n">
         <v>3.4334</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W28" t="n">
         <v>5.374099999999999</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X28" t="n">
         <v>-1.9405</v>
       </c>
+      <c r="Y28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
